--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484571_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484571_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2973</v>
+        <v>2.119</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4833</v>
+        <v>3.1564</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.186</v>
+        <v>-1.0374</v>
       </c>
       <c r="G2" t="n">
         <v>1.8009</v>
@@ -610,13 +610,13 @@
         <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1475</v>
+        <v>-0.3258</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8627</v>
+        <v>-0.1896</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2848</v>
+        <v>-0.1361</v>
       </c>
       <c r="V2" t="n">
         <v>0.6439</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0951</v>
+        <v>1.1254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5373</v>
+        <v>0.5923</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5578</v>
+        <v>0.533</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7941</v>
@@ -688,13 +688,13 @@
         <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4931</v>
+        <v>-0.4629</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1297</v>
+        <v>-0.0746</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3634</v>
+        <v>-0.3882</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9278</v>
+        <v>1.0325</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1154</v>
+        <v>1.2945</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1876</v>
+        <v>-0.2619</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3055</v>
@@ -766,13 +766,13 @@
         <v>2.0158</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7826</v>
+        <v>-0.6778</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5151</v>
+        <v>-0.336</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2675</v>
+        <v>-0.3418</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>J. SÁEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4861</v>
+        <v>0.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5106</v>
+        <v>0.3251</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0245</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.993</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6337</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3593</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2906</v>
+        <v>0.3251</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2072</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2836</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8409</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4427</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5628</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1705</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3924</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SÁEZ GONZÁLEZ</t>
+          <t>T. ROIG ARIÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. ROIG ARIÑO</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3251</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3251</v>
+        <v>1.6041</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-2.3465</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3251</v>
+        <v>-1.993</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3251</v>
+        <v>-0.6337</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.3593</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3251</v>
+        <v>1.2906</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3251</v>
+        <v>1.2072</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-3.2836</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.8409</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.4427</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.3343</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.264</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0703</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.9658</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0247</v>
+        <v>-0.9746</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3611</v>
+        <v>-2.4844</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3364</v>
+        <v>1.5098</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7911</v>
@@ -1078,13 +1078,13 @@
         <v>3.1154</v>
       </c>
       <c r="S8" t="n">
-        <v>0.133</v>
+        <v>0.1831</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2542</v>
+        <v>0.1309</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1212</v>
+        <v>0.0522</v>
       </c>
       <c r="V8" t="n">
         <v>1.267</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8496</v>
+        <v>-1.3767</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4943</v>
+        <v>2.8929</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3439</v>
+        <v>-4.2696</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8908</v>
@@ -1156,13 +1156,13 @@
         <v>3.2986</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7468</v>
+        <v>-1.2739</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6621</v>
+        <v>-0.2635</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0847</v>
+        <v>-1.0104</v>
       </c>
       <c r="V9" t="n">
         <v>0.3219</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9817</v>
+        <v>-1.822</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1769</v>
+        <v>-0.0668</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8048</v>
+        <v>-1.7553</v>
       </c>
       <c r="G10" t="n">
         <v>-0.07729999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>0.1833</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1872</v>
+        <v>-0.0275</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2202</v>
+        <v>-0.1101</v>
       </c>
       <c r="U10" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9005</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ANTONI RODRIGUEZ</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0673</v>
+        <v>-2.041</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1051</v>
+        <v>-0.5164</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0379</v>
+        <v>-1.5247</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1255</v>
+        <v>-0.5924</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5101</v>
+        <v>-0.7623</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3846</v>
+        <v>0.1699</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5546</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5546</v>
+        <v>0.5077</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.0098</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5709</v>
+        <v>-1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9555</v>
+        <v>-1.27</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3846</v>
+        <v>0.16</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3083</v>
+        <v>-0.9434</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5505</v>
+        <v>-0.4683</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2422</v>
+        <v>-0.4751</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>M. ANTONI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1453</v>
+        <v>-2.0618</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8188</v>
+        <v>-2.0501</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3265</v>
+        <v>-0.0117</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5924</v>
+        <v>-2.1255</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7623</v>
+        <v>-2.5101</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1699</v>
+        <v>0.3846</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5175999999999999</v>
+        <v>-1.5546</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5077</v>
+        <v>-1.5546</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0098</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.11</v>
+        <v>-0.5709</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.27</v>
+        <v>-0.9555</v>
       </c>
       <c r="O12" t="n">
-        <v>0.16</v>
+        <v>0.3846</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0477</v>
+        <v>-0.3028</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.4955</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2769</v>
+        <v>0.1927</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5518</v>
+        <v>-2.1998</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9878</v>
+        <v>-1.6854</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5144</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7055</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.663</v>
+        <v>-0.3111</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6606</v>
+        <v>-0.3582</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0024</v>
+        <v>0.0471</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.9556</v>
+        <v>-3.5816</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2898</v>
+        <v>-2.7672</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6657</v>
+        <v>-0.8144</v>
       </c>
       <c r="G14" t="n">
         <v>-1.3752</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.308</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1561</v>
+        <v>-0.6335</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1519</v>
+        <v>-0.3005</v>
       </c>
       <c r="V14" t="n">
         <v>0.0104</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.1329</v>
+        <v>-3.7279</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.8124</v>
+        <v>-2.7295</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3205</v>
+        <v>-0.9984</v>
       </c>
       <c r="G15" t="n">
         <v>-3.0346</v>
@@ -1624,13 +1624,13 @@
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5198</v>
+        <v>-0.1148</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2217</v>
+        <v>-0.1387</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2981</v>
+        <v>0.0239</v>
       </c>
       <c r="V15" t="n">
         <v>-0.945</v>
@@ -1657,28 +1657,28 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-15.2524</v>
+        <v>-13.6007</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.7608</v>
+        <v>-2.109399999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.4914</v>
+        <v>-11.4915</v>
       </c>
       <c r="G16" t="n">
         <v>-14.2339</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.059600000000001</v>
+        <v>-6.0596</v>
       </c>
       <c r="I16" t="n">
-        <v>-8.174299999999999</v>
+        <v>-8.174300000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>5.971300000000003</v>
+        <v>5.971300000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>8.212600000000002</v>
+        <v>8.2126</v>
       </c>
       <c r="L16" t="n">
         <v>-2.2415</v>
@@ -1693,7 +1693,7 @@
         <v>-5.932899999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>6.413900000000001</v>
+        <v>6.4139</v>
       </c>
       <c r="Q16" t="n">
         <v>-14.6608</v>
@@ -1702,10 +1702,10 @@
         <v>21.0746</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.5082</v>
+        <v>-4.856599999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.3247</v>
+        <v>-2.6731</v>
       </c>
       <c r="U16" t="n">
         <v>-2.1833</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.2976</v>
+        <v>8.3903</v>
       </c>
       <c r="E17" t="n">
-        <v>9.296799999999999</v>
+        <v>10.1622</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9992</v>
+        <v>-1.7719</v>
       </c>
       <c r="G17" t="n">
         <v>4.2339</v>
@@ -1780,13 +1780,13 @@
         <v>2.3823</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1428</v>
+        <v>-0.0502</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.138</v>
+        <v>-0.2726</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0049</v>
+        <v>0.2224</v>
       </c>
       <c r="V17" t="n">
         <v>4.7563</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5869</v>
+        <v>3.8642</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5863</v>
+        <v>1.3397</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0005999999999999999</v>
+        <v>2.5245</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3415</v>
+        <v>3.1399</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3384</v>
+        <v>-1.5047</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0031</v>
+        <v>4.6446</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5372</v>
+        <v>3.8823</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6621</v>
+        <v>-0.8269</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8752</v>
+        <v>4.7092</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1958</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3237</v>
+        <v>-0.6778</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1279</v>
+        <v>-0.0646</v>
       </c>
       <c r="P18" t="n">
-        <v>0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0995</v>
+        <v>-3.8484</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8326</v>
+        <v>2.9321</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1013</v>
+        <v>1.0175</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1486</v>
+        <v>0.0389</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0473</v>
+        <v>0.9787</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5889</v>
+        <v>0.6231</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5889</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>J. MATEO LAZARO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.3296</v>
+        <v>2.9656</v>
       </c>
       <c r="E19" t="n">
-        <v>0.859</v>
+        <v>1.7619</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4706</v>
+        <v>1.2037</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1399</v>
+        <v>3.6939</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5047</v>
+        <v>2.4889</v>
       </c>
       <c r="I19" t="n">
-        <v>4.6446</v>
+        <v>1.2051</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8823</v>
+        <v>2.5417</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8269</v>
+        <v>2.4584</v>
       </c>
       <c r="L19" t="n">
-        <v>4.7092</v>
+        <v>0.0833</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7423999999999999</v>
+        <v>1.1522</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6778</v>
+        <v>0.0305</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0646</v>
+        <v>1.1217</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9163</v>
+        <v>0.9163</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8484</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9321</v>
+        <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4829</v>
+        <v>-0.0453</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4419</v>
+        <v>-0.4683</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9248</v>
+        <v>0.4231</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6231</v>
+        <v>-1.5993</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>-0.3115</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6439</v>
+        <v>-1.2878</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.0025</v>
+        <v>2.9009</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2939</v>
+        <v>2.9009</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7086</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3983</v>
+        <v>2.9009</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9625</v>
+        <v>2.2758</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4358</v>
+        <v>0.6251</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2321</v>
+        <v>2.9009</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1487</v>
+        <v>2.2758</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0833</v>
+        <v>0.6251</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1662</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1863</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3525</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1931</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0618</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1313</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.9009</v>
+        <v>2.6252</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9009</v>
+        <v>1.8132</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9009</v>
+        <v>1.3983</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2758</v>
+        <v>0.9625</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6251</v>
+        <v>0.4358</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9009</v>
+        <v>1.2321</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2758</v>
+        <v>1.1487</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6251</v>
+        <v>0.0833</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.1662</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.1863</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.3525</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.8158</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.2347</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MATEO LAZARO</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.8724</v>
+        <v>2.3777</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5696</v>
+        <v>1.9648</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3028</v>
+        <v>0.4128</v>
       </c>
       <c r="G22" t="n">
-        <v>3.6939</v>
+        <v>1.4477</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4889</v>
+        <v>0.1462</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2051</v>
+        <v>1.3015</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5417</v>
+        <v>1.7454</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4584</v>
+        <v>0.4118</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0833</v>
+        <v>1.3336</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1522</v>
+        <v>-0.2977</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0305</v>
+        <v>-0.2656</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1217</v>
+        <v>-0.0321</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1385</v>
+        <v>0.197</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6606</v>
+        <v>0.2195</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5222</v>
+        <v>-0.0224</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5993</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.0179</v>
+        <v>1.5254</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5802</v>
+        <v>1.4709</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4376</v>
+        <v>0.0545</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4477</v>
+        <v>1.3415</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1462</v>
+        <v>0.3384</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3015</v>
+        <v>1.0031</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7454</v>
+        <v>1.5372</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4118</v>
+        <v>0.6621</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3336</v>
+        <v>0.8752</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2977</v>
+        <v>-0.1958</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2656</v>
+        <v>-0.3237</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0321</v>
+        <v>0.1279</v>
       </c>
       <c r="P23" t="n">
         <v>0.733</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R23" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1628</v>
+        <v>1.0398</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1652</v>
+        <v>1.0332</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0023</v>
+        <v>0.0066</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="24">
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>M. REOS CAMPOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.137</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2687</v>
+        <v>0.1226</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1694</v>
+        <v>-0.2596</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6123</v>
+        <v>1.2202</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4552</v>
+        <v>1.3996</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1571</v>
+        <v>-0.1794</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6505</v>
+        <v>1.9698</v>
       </c>
       <c r="K25" t="n">
-        <v>1.5573</v>
+        <v>2.5017</v>
       </c>
       <c r="L25" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.5319</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0382</v>
+        <v>-0.7496</v>
       </c>
       <c r="N25" t="n">
         <v>-1.1021</v>
       </c>
       <c r="O25" t="n">
-        <v>0.064</v>
+        <v>0.3525</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.5656</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6207</v>
+        <v>0.2475</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3175</v>
+        <v>-0.0147</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3031</v>
+        <v>0.2622</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.5681</v>
+        <v>-0.3219</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.5339</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. REOS CAMPOS</t>
+          <t>A. RUIZ FRAGUEIRO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9689</v>
+        <v>-1.3798</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3582</v>
+        <v>-2.1477</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6107</v>
+        <v>0.7679</v>
       </c>
       <c r="G26" t="n">
-        <v>1.2202</v>
+        <v>-3.4153</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3996</v>
+        <v>-0.0018</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1794</v>
+        <v>-3.4135</v>
       </c>
       <c r="J26" t="n">
-        <v>1.9698</v>
+        <v>-1.4063</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5017</v>
+        <v>1.6223</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5319</v>
+        <v>-3.0286</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.7496</v>
+        <v>-2.0091</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.1021</v>
+        <v>-1.6241</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3525</v>
+        <v>-0.3849</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.2828</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.8326</v>
+        <v>-2.0158</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5844</v>
+        <v>1.6403</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4955</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.08890000000000001</v>
+        <v>1.0098</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.3219</v>
+        <v>0.945</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.3219</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A. RUIZ FRAGUEIRO</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.8577</v>
+        <v>-2.0139</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.7247</v>
+        <v>-0.5967</v>
       </c>
       <c r="F27" t="n">
-        <v>0.867</v>
+        <v>-1.4172</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.4153</v>
+        <v>0.6123</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0018</v>
+        <v>0.4552</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.4135</v>
+        <v>0.1571</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.4063</v>
+        <v>1.6505</v>
       </c>
       <c r="K27" t="n">
-        <v>1.6223</v>
+        <v>1.5573</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.0286</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.0091</v>
+        <v>-1.0382</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.6241</v>
+        <v>-1.1021</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3849</v>
+        <v>0.064</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.5498</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.0158</v>
+        <v>-3.6651</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S27" t="n">
-        <v>1.1624</v>
+        <v>1.5075</v>
       </c>
       <c r="T27" t="n">
-        <v>0.0536</v>
+        <v>0.4521</v>
       </c>
       <c r="U27" t="n">
-        <v>1.1089</v>
+        <v>1.0554</v>
       </c>
       <c r="V27" t="n">
-        <v>0.945</v>
+        <v>-1.5681</v>
       </c>
       <c r="W27" t="n">
-        <v>0.6439</v>
+        <v>0.9658</v>
       </c>
       <c r="X27" t="n">
-        <v>0.3011</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="28">
@@ -2593,10 +2593,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.74</v>
+        <v>-2.5477</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.6689</v>
+        <v>-3.4766</v>
       </c>
       <c r="F28" t="n">
         <v>0.9288999999999999</v>
@@ -2638,10 +2638,10 @@
         <v>0.9163</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5686</v>
+        <v>0.7609</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.0746</v>
+        <v>0.1177</v>
       </c>
       <c r="U28" t="n">
         <v>0.6433</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.2384</v>
+        <v>-3.6279</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.0624</v>
+        <v>-4.774</v>
       </c>
       <c r="F29" t="n">
-        <v>0.824</v>
+        <v>1.1461</v>
       </c>
       <c r="G29" t="n">
         <v>-1.8136</v>
@@ -2716,13 +2716,13 @@
         <v>1.0995</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.0183</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.4223</v>
+        <v>-0.1338</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1699</v>
+        <v>0.1521</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>15.2523</v>
+        <v>15.8932</v>
       </c>
       <c r="E30" t="n">
         <v>11.4914</v>
       </c>
       <c r="F30" t="n">
-        <v>3.7608</v>
+        <v>4.401700000000001</v>
       </c>
       <c r="G30" t="n">
         <v>14.2339</v>
@@ -2764,7 +2764,7 @@
         <v>6.059699999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>8.174200000000003</v>
+        <v>8.174199999999999</v>
       </c>
       <c r="J30" t="n">
         <v>20.2051</v>
@@ -2794,22 +2794,22 @@
         <v>14.6605</v>
       </c>
       <c r="S30" t="n">
-        <v>6.5083</v>
+        <v>7.149100000000001</v>
       </c>
       <c r="T30" t="n">
-        <v>2.183400000000001</v>
+        <v>2.1836</v>
       </c>
       <c r="U30" t="n">
-        <v>4.3249</v>
+        <v>4.9659</v>
       </c>
       <c r="V30" t="n">
-        <v>0.9243000000000008</v>
+        <v>0.9243000000000003</v>
       </c>
       <c r="W30" t="n">
         <v>10.1774</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.253099999999998</v>
+        <v>-9.2531</v>
       </c>
     </row>
   </sheetData>
